--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_Teste_Diagnostic.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_Teste_Diagnostic.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,14 +379,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shapiro-Wilk (Normalitate)</t>
+          <t>Shapiro-Wilk</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.8586806456511329</v>
+        <v>0.8451678766416189</v>
       </c>
       <c r="C2">
-        <v>0.002105958821717603</v>
+        <v>0.0002669699797993587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -397,52 +397,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jarque-Bera (Normalitate)</t>
+          <t>Breusch-Pagan</t>
         </is>
       </c>
       <c r="B3">
-        <v>25.70152209191753</v>
+        <v>12.46352243494252</v>
       </c>
       <c r="C3">
-        <v>2.624130260975299E-06</v>
+        <v>0.02895985037275483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ne-normal</t>
+          <t>Heteroscedastic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Breusch-Pagan (Heteroscedasticitate)</t>
+          <t>Durbin-Watson</t>
         </is>
       </c>
       <c r="B4">
-        <v>1.67601407100087</v>
+        <v>2.052511515113448</v>
       </c>
       <c r="C4">
-        <v>0.946957961270809</v>
+        <v>0.5780891643869835</v>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>Homoscedastic</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Durbin-Watson (Autocorelare)</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>2.368897492949107</v>
-      </c>
-      <c r="C5">
-        <v>0.7946432182397458</v>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t>Fara Autocorelare</t>
         </is>
